--- a/hoagland_recipes/NxPxI_hoagland_lowN_revised.xlsx
+++ b/hoagland_recipes/NxPxI_hoagland_lowN_revised.xlsx
@@ -8,19 +8,185 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eaperkowski/git/2026_NxPxI/hoagland_recipes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E719067E-5725-BF41-BD5C-318A9C709660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC95845-3385-D94B-9EF5-0D525BE9569E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="600" windowWidth="30180" windowHeight="28200" activeTab="5" xr2:uid="{D8162C4C-0F91-B749-8466-88C5F33C3EA0}"/>
+    <workbookView xWindow="24420" yWindow="600" windowWidth="42060" windowHeight="28200" activeTab="5" xr2:uid="{D8162C4C-0F91-B749-8466-88C5F33C3EA0}"/>
   </bookViews>
   <sheets>
     <sheet name="70 ppm N, 0 ppm P" sheetId="1" r:id="rId1"/>
     <sheet name="70 ppm N, 7.5 ppm P" sheetId="2" r:id="rId2"/>
     <sheet name="70 ppm N, 15 ppm P" sheetId="3" r:id="rId3"/>
     <sheet name="70 ppm N, 31 ppm P" sheetId="4" r:id="rId4"/>
-    <sheet name="70 ppm N, 62 ppm P" sheetId="5" r:id="rId5"/>
-    <sheet name="70 ppm N, 93 ppm P" sheetId="6" r:id="rId6"/>
+    <sheet name="70 ppm N, 46.5 ppm P" sheetId="6" r:id="rId5"/>
+    <sheet name="70 ppm N, 62 ppm P" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$D$3:$D$6,'70 ppm N, 0 ppm P'!$D$10:$D$13</definedName>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$D$3:$D$6,'70 ppm N, 31 ppm P'!$D$10:$D$14</definedName>
+    <definedName name="solver_adj" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$D$3:$D$6,'70 ppm N, 46.5 ppm P'!$D$10:$D$13</definedName>
+    <definedName name="solver_adj" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$D$3:$D$6,'70 ppm N, 62 ppm P'!$D$10:$D$13</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="4" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$B$39</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$B$39</definedName>
+    <definedName name="solver_lhs1" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$B$39</definedName>
+    <definedName name="solver_lhs1" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$B$39</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$B$40</definedName>
+    <definedName name="solver_lhs2" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$B$40</definedName>
+    <definedName name="solver_lhs2" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$B$40</definedName>
+    <definedName name="solver_lhs2" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$B$40</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$B$41</definedName>
+    <definedName name="solver_lhs3" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$B$41</definedName>
+    <definedName name="solver_lhs3" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$B$41</definedName>
+    <definedName name="solver_lhs3" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$B$41</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$B$42</definedName>
+    <definedName name="solver_lhs4" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$B$42</definedName>
+    <definedName name="solver_lhs4" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$B$42</definedName>
+    <definedName name="solver_lhs4" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$B$42</definedName>
+    <definedName name="solver_lhs5" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$B$43</definedName>
+    <definedName name="solver_lhs5" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$B$43</definedName>
+    <definedName name="solver_lhs6" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$B$44</definedName>
+    <definedName name="solver_lhs6" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$B$44</definedName>
+    <definedName name="solver_lin" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_lin" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_lin" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_lin" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="4" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="4" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">6</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">6</definedName>
+    <definedName name="solver_num" localSheetId="4" hidden="1">4</definedName>
+    <definedName name="solver_num" localSheetId="5" hidden="1">4</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$B$56</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$B$56</definedName>
+    <definedName name="solver_opt" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$B$56</definedName>
+    <definedName name="solver_opt" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$B$56</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.001</definedName>
+    <definedName name="solver_pre" localSheetId="3" hidden="1">0.001</definedName>
+    <definedName name="solver_pre" localSheetId="4" hidden="1">0.001</definedName>
+    <definedName name="solver_pre" localSheetId="5" hidden="1">0.001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rel4" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel4" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rel4" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_rel4" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rel5" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel5" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rel6" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel6" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$C$39</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$C$39</definedName>
+    <definedName name="solver_rhs1" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$C$39</definedName>
+    <definedName name="solver_rhs1" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$C$39</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$C$40</definedName>
+    <definedName name="solver_rhs2" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$C$40</definedName>
+    <definedName name="solver_rhs2" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$C$40</definedName>
+    <definedName name="solver_rhs2" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$C$40</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$C$41</definedName>
+    <definedName name="solver_rhs3" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$C$41</definedName>
+    <definedName name="solver_rhs3" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$C$41</definedName>
+    <definedName name="solver_rhs3" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$C$41</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$C$42</definedName>
+    <definedName name="solver_rhs4" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$C$42</definedName>
+    <definedName name="solver_rhs4" localSheetId="4" hidden="1">'70 ppm N, 46.5 ppm P'!$C$42</definedName>
+    <definedName name="solver_rhs4" localSheetId="5" hidden="1">'70 ppm N, 62 ppm P'!$C$42</definedName>
+    <definedName name="solver_rhs5" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$C$43</definedName>
+    <definedName name="solver_rhs5" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$C$43</definedName>
+    <definedName name="solver_rhs6" localSheetId="0" hidden="1">'70 ppm N, 0 ppm P'!$C$44</definedName>
+    <definedName name="solver_rhs6" localSheetId="3" hidden="1">'70 ppm N, 31 ppm P'!$C$44</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="4" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="5" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="4" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="5" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">3</definedName>
+    <definedName name="solver_typ" localSheetId="4" hidden="1">3</definedName>
+    <definedName name="solver_typ" localSheetId="5" hidden="1">3</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0.25</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0.25</definedName>
+    <definedName name="solver_val" localSheetId="4" hidden="1">0.25</definedName>
+    <definedName name="solver_val" localSheetId="5" hidden="1">0.25</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="5" hidden="1">2</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="59">
   <si>
     <t>Primary N addition compounds</t>
   </si>
@@ -736,15 +902,46 @@
   <si>
     <t>Projected pH range:</t>
   </si>
+  <si>
+    <t>Calculate NH4:NO3 ratio</t>
+  </si>
+  <si>
+    <t>mL per L</t>
+  </si>
+  <si>
+    <t>mM</t>
+  </si>
+  <si>
+    <t>NH4 from NH4H2PO4</t>
+  </si>
+  <si>
+    <t>NO3 from KNO3</t>
+  </si>
+  <si>
+    <t>NO3 from Ca(NO3)2</t>
+  </si>
+  <si>
+    <t>NH4 from NH4NO3</t>
+  </si>
+  <si>
+    <t>NO3 from NH4NO3</t>
+  </si>
+  <si>
+    <t>NH4:NO3 ratio</t>
+  </si>
+  <si>
+    <t>target_ppm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -771,6 +968,20 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -799,12 +1010,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1139,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D79FAAB-8098-D94B-8628-DB10C053BFE5}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -1217,11 +1433,11 @@
         <v>164.08799999999999</v>
       </c>
       <c r="D5">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="0"/>
-        <v>180.49680000000001</v>
+        <v>147.67920000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -1235,11 +1451,11 @@
         <v>80.043000000000006</v>
       </c>
       <c r="D6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>64.034400000000005</v>
+        <v>80.043000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1333,11 +1549,11 @@
         <v>110.98</v>
       </c>
       <c r="D13">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>310.74399999999997</v>
+        <v>344.03800000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -1431,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <f>IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
+        <f t="shared" ref="E20:E31" si="1">IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1450,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <f>IFERROR((C21*1000)/(1000/(B21*D21)), 0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1469,7 +1685,7 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="2">
-        <f>IFERROR((C22*1000)/(1000/(B22*D22)), 0)</f>
+        <f t="shared" si="1"/>
         <v>46.913159999999991</v>
       </c>
     </row>
@@ -1488,7 +1704,7 @@
         <v>0.6</v>
       </c>
       <c r="E23" s="2">
-        <f>IFERROR((C23*1000)/(1000/(B23*D23)), 0)</f>
+        <f t="shared" si="1"/>
         <v>16.807199999999998</v>
       </c>
     </row>
@@ -1504,11 +1720,11 @@
       </c>
       <c r="D24">
         <f>D5</f>
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E24" s="2">
-        <f>IFERROR((C24*1000)/(1000/(B24*D24)), 0)</f>
-        <v>44.085800000000006</v>
+        <f t="shared" si="1"/>
+        <v>36.0702</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -1523,11 +1739,11 @@
       </c>
       <c r="D25">
         <f>D5</f>
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E25" s="2">
-        <f>IFERROR((C25*1000)/(1000/(B25*D25)), 0)</f>
-        <v>30.813200000000002</v>
+        <f t="shared" si="1"/>
+        <v>25.210799999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -1542,11 +1758,11 @@
       </c>
       <c r="D26">
         <f>D6</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2">
-        <f>IFERROR((C26*1000)/(1000/(B26*D26)), 0)</f>
-        <v>22.409600000000001</v>
+        <f t="shared" si="1"/>
+        <v>28.012</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -1564,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="2">
-        <f>IFERROR((C27*1000)/(1000/(B27*D27)), 0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1583,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="2">
-        <f>IFERROR((C28*1000)/(1000/(B28*D28)), 0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1602,7 +1818,7 @@
         <v>2.8</v>
       </c>
       <c r="E29" s="2">
-        <f>IFERROR((C29*1000)/(1000/(B29*D29)), 0)</f>
+        <f t="shared" si="1"/>
         <v>109.46403999999998</v>
       </c>
     </row>
@@ -1621,7 +1837,7 @@
         <v>2.8</v>
       </c>
       <c r="E30" s="2">
-        <f>IFERROR((C30*1000)/(1000/(B30*D30)), 0)</f>
+        <f t="shared" si="1"/>
         <v>99.2684</v>
       </c>
     </row>
@@ -1640,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="2">
-        <f>IFERROR((C31*1000)/(1000/(B31*D31)), 0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1656,11 +1872,11 @@
       </c>
       <c r="D32">
         <f>D13</f>
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32:E33" si="1">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
-        <v>112.21839999999999</v>
+        <f t="shared" ref="E32:E33" si="2">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
+        <v>124.24180000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1671,15 +1887,16 @@
         <v>1</v>
       </c>
       <c r="C33">
-        <v>35.453000000000003</v>
+        <f>C30*2</f>
+        <v>70.906000000000006</v>
       </c>
       <c r="D33">
         <f>D13</f>
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="1"/>
-        <v>99.2684</v>
+        <f t="shared" si="2"/>
+        <v>219.80860000000001</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -1697,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" ref="E34" si="2">IFERROR((C34*1000)/(1000/(B34*D34)), 0)</f>
+        <f t="shared" ref="E34" si="3">IFERROR((C34*1000)/(1000/(B34*D34)), 0)</f>
         <v>48.61</v>
       </c>
     </row>
@@ -1733,7 +1950,7 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
@@ -1747,11 +1964,12 @@
         <f>SUM(E20,E23,E25,E26)</f>
         <v>70.03</v>
       </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>18</v>
+      <c r="C39" s="2">
+        <v>70</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" ref="D39:D44" si="4">C39-B39</f>
+        <v>-3.0000000000001137E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1762,11 +1980,12 @@
         <f>SUM(E21,E28)</f>
         <v>0</v>
       </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
+      <c r="C40" s="2">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1781,7 +2000,7 @@
         <v>156.4</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" ref="D41:D44" si="3">C41-B41</f>
+        <f t="shared" si="4"/>
         <v>2.2800000000046339E-2</v>
       </c>
     </row>
@@ -1791,14 +2010,14 @@
       </c>
       <c r="B42" s="2">
         <f>E31+E24+E32</f>
-        <v>156.30419999999998</v>
+        <v>160.31200000000001</v>
       </c>
       <c r="C42">
         <v>160.30000000000001</v>
       </c>
       <c r="D42" s="2">
-        <f t="shared" si="3"/>
-        <v>3.9958000000000311</v>
+        <f t="shared" si="4"/>
+        <v>-1.2000000000000455E-2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1813,7 +2032,7 @@
         <v>48.6</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-9.9999999999980105E-3</v>
       </c>
     </row>
@@ -1829,7 +2048,7 @@
         <v>64.099999999999994</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.0000000000001137E-2</v>
       </c>
     </row>
@@ -1838,7 +2057,115 @@
         <v>47</v>
       </c>
       <c r="B46" s="3">
-        <v>6.15</v>
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <f>B50*C50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <f>D4</f>
+        <v>0.6</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ref="D51:D54" si="5">B51*C51</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <f>D5</f>
+        <v>0.45</v>
+      </c>
+      <c r="D52">
+        <f>B52*C52*2</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f>D6</f>
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <f>D6</f>
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56">
+        <f>IFERROR((D50+D53)/(D51+D52+D54), 0)</f>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1848,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E3AFEC2-0431-2C4C-BD04-E469597BD0C8}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
@@ -1924,11 +2251,11 @@
         <v>164.08799999999999</v>
       </c>
       <c r="D5">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E5" s="2">
         <f>IFERROR((C5*1000)/(1000/(B5*D5)), 0)</f>
-        <v>180.49680000000001</v>
+        <v>147.67920000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -1942,11 +2269,11 @@
         <v>80.043000000000006</v>
       </c>
       <c r="D6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>64.034400000000005</v>
+        <v>80.043000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -2040,11 +2367,11 @@
         <v>110.98</v>
       </c>
       <c r="D13">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>321.84199999999998</v>
+        <v>344.03800000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2138,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <f>IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
+        <f t="shared" ref="E20:E31" si="1">IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2157,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <f>IFERROR((C21*1000)/(1000/(B21*D21)), 0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2176,7 +2503,7 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="2">
-        <f>IFERROR((C22*1000)/(1000/(B22*D22)), 0)</f>
+        <f t="shared" si="1"/>
         <v>46.913159999999991</v>
       </c>
     </row>
@@ -2195,7 +2522,7 @@
         <v>0.6</v>
       </c>
       <c r="E23" s="2">
-        <f>IFERROR((C23*1000)/(1000/(B23*D23)), 0)</f>
+        <f t="shared" si="1"/>
         <v>16.807199999999998</v>
       </c>
     </row>
@@ -2211,11 +2538,11 @@
       </c>
       <c r="D24">
         <f>D5</f>
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E24" s="2">
-        <f>IFERROR((C24*1000)/(1000/(B24*D24)), 0)</f>
-        <v>44.085800000000006</v>
+        <f t="shared" si="1"/>
+        <v>36.0702</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2230,11 +2557,11 @@
       </c>
       <c r="D25">
         <f>D5</f>
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E25" s="2">
-        <f>IFERROR((C25*1000)/(1000/(B25*D25)), 0)</f>
-        <v>30.813200000000002</v>
+        <f t="shared" si="1"/>
+        <v>25.210799999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2249,11 +2576,11 @@
       </c>
       <c r="D26">
         <f>D6</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2">
-        <f>IFERROR((C26*1000)/(1000/(B26*D26)), 0)</f>
-        <v>22.409600000000001</v>
+        <f t="shared" si="1"/>
+        <v>28.012</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2271,7 +2598,7 @@
         <v>0.25</v>
       </c>
       <c r="E27" s="2">
-        <f>IFERROR((C27*1000)/(1000/(B27*D27)), 0)</f>
+        <f t="shared" si="1"/>
         <v>9.7735749999999992</v>
       </c>
     </row>
@@ -2290,7 +2617,7 @@
         <v>0.25</v>
       </c>
       <c r="E28" s="2">
-        <f>IFERROR((C28*1000)/(1000/(B28*D28)), 0)</f>
+        <f t="shared" si="1"/>
         <v>7.7434250000000002</v>
       </c>
     </row>
@@ -2309,7 +2636,7 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="E29" s="2">
-        <f>IFERROR((C29*1000)/(1000/(B29*D29)), 0)</f>
+        <f t="shared" si="1"/>
         <v>99.690464999999975</v>
       </c>
     </row>
@@ -2328,7 +2655,7 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="E30" s="2">
-        <f>IFERROR((C30*1000)/(1000/(B30*D30)), 0)</f>
+        <f t="shared" si="1"/>
         <v>90.405149999999992</v>
       </c>
     </row>
@@ -2347,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="2">
-        <f>IFERROR((C31*1000)/(1000/(B31*D31)), 0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2363,11 +2690,11 @@
       </c>
       <c r="D32">
         <f>D13</f>
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32:E34" si="1">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
-        <v>116.22619999999999</v>
+        <f t="shared" ref="E32:E34" si="2">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
+        <v>124.24180000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -2378,15 +2705,16 @@
         <v>1</v>
       </c>
       <c r="C33">
-        <v>35.453000000000003</v>
+        <f>C30*2</f>
+        <v>70.906000000000006</v>
       </c>
       <c r="D33">
         <f>D13</f>
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="1"/>
-        <v>102.8137</v>
+        <f t="shared" si="2"/>
+        <v>219.80860000000001</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2404,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48.61</v>
       </c>
     </row>
@@ -2440,7 +2768,7 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
@@ -2454,26 +2782,28 @@
         <f>SUM(E20,E23,E25,E26)</f>
         <v>70.03</v>
       </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>18</v>
+      <c r="C39" s="2">
+        <v>70</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" ref="D39:D44" si="3">C39-B39</f>
+        <v>-3.0000000000001137E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="8">
         <f>SUM(E21,E28)</f>
         <v>7.7434250000000002</v>
       </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
+      <c r="C40">
+        <v>7.75</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="3"/>
+        <v>6.5749999999997755E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -2488,7 +2818,7 @@
         <v>156.4</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" ref="D41:D44" si="2">C41-B41</f>
+        <f t="shared" si="3"/>
         <v>2.2800000000046339E-2</v>
       </c>
     </row>
@@ -2504,7 +2834,7 @@
         <v>160.30000000000001</v>
       </c>
       <c r="D42" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.2000000000000455E-2</v>
       </c>
     </row>
@@ -2520,7 +2850,7 @@
         <v>48.6</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-9.9999999999980105E-3</v>
       </c>
     </row>
@@ -2536,7 +2866,7 @@
         <v>64.099999999999994</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.0000000000001137E-2</v>
       </c>
     </row>
@@ -2546,6 +2876,114 @@
       </c>
       <c r="B46" s="3">
         <v>6.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <f>B50*C50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <f>D4</f>
+        <v>0.6</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ref="D51:D54" si="4">B51*C51</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <f>D5</f>
+        <v>0.45</v>
+      </c>
+      <c r="D52">
+        <f>B52*C52*2</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f>D6</f>
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <f>D6</f>
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="7">
+        <f>IFERROR((D50+D53)/(D51+D52+D54), 0)</f>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -2555,7 +2993,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABB501D-9163-9545-8859-8445093C95AF}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
@@ -2631,11 +3069,11 @@
         <v>164.08799999999999</v>
       </c>
       <c r="D5">
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E5" s="2">
         <f>IFERROR((C5*1000)/(1000/(B5*D5)), 0)</f>
-        <v>180.49680000000001</v>
+        <v>147.67920000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2649,11 +3087,11 @@
         <v>80.043000000000006</v>
       </c>
       <c r="D6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>64.034400000000005</v>
+        <v>80.043000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -2729,11 +3167,11 @@
         <v>100.087</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10.008699999999999</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2747,11 +3185,11 @@
         <v>110.98</v>
       </c>
       <c r="D13">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>321.84199999999998</v>
+        <v>332.94</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2845,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <f>IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
+        <f t="shared" ref="E20:E31" si="1">IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2864,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <f>IFERROR((C21*1000)/(1000/(B21*D21)), 0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2883,7 +3321,7 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="2">
-        <f>IFERROR((C22*1000)/(1000/(B22*D22)), 0)</f>
+        <f t="shared" si="1"/>
         <v>46.913159999999991</v>
       </c>
     </row>
@@ -2902,7 +3340,7 @@
         <v>0.6</v>
       </c>
       <c r="E23" s="2">
-        <f>IFERROR((C23*1000)/(1000/(B23*D23)), 0)</f>
+        <f t="shared" si="1"/>
         <v>16.807199999999998</v>
       </c>
     </row>
@@ -2918,11 +3356,11 @@
       </c>
       <c r="D24">
         <f>D5</f>
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E24" s="2">
-        <f>IFERROR((C24*1000)/(1000/(B24*D24)), 0)</f>
-        <v>44.085800000000006</v>
+        <f t="shared" si="1"/>
+        <v>36.0702</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2937,11 +3375,11 @@
       </c>
       <c r="D25">
         <f>D5</f>
-        <v>0.55000000000000004</v>
+        <v>0.45</v>
       </c>
       <c r="E25" s="2">
-        <f>IFERROR((C25*1000)/(1000/(B25*D25)), 0)</f>
-        <v>30.813200000000002</v>
+        <f t="shared" si="1"/>
+        <v>25.210799999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2956,11 +3394,11 @@
       </c>
       <c r="D26">
         <f>D6</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2">
-        <f>IFERROR((C26*1000)/(1000/(B26*D26)), 0)</f>
-        <v>22.409600000000001</v>
+        <f t="shared" si="1"/>
+        <v>28.012</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -2978,7 +3416,7 @@
         <v>0.5</v>
       </c>
       <c r="E27" s="2">
-        <f>IFERROR((C27*1000)/(1000/(B27*D27)), 0)</f>
+        <f t="shared" si="1"/>
         <v>19.547149999999998</v>
       </c>
     </row>
@@ -2997,7 +3435,7 @@
         <v>0.5</v>
       </c>
       <c r="E28" s="2">
-        <f>IFERROR((C28*1000)/(1000/(B28*D28)), 0)</f>
+        <f t="shared" si="1"/>
         <v>15.48685</v>
       </c>
     </row>
@@ -3016,7 +3454,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="E29" s="2">
-        <f>IFERROR((C29*1000)/(1000/(B29*D29)), 0)</f>
+        <f t="shared" si="1"/>
         <v>89.916889999999981</v>
       </c>
     </row>
@@ -3035,7 +3473,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="E30" s="2">
-        <f>IFERROR((C30*1000)/(1000/(B30*D30)), 0)</f>
+        <f t="shared" si="1"/>
         <v>81.541899999999998</v>
       </c>
     </row>
@@ -3051,11 +3489,11 @@
       </c>
       <c r="D31">
         <f>D12</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E31" s="2">
-        <f>IFERROR((C31*1000)/(1000/(B31*D31)), 0)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>4.0077999999999996</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -3070,11 +3508,11 @@
       </c>
       <c r="D32">
         <f>D13</f>
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32:E34" si="1">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
-        <v>116.22619999999999</v>
+        <f t="shared" ref="E32:E34" si="2">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
+        <v>120.23400000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -3085,15 +3523,16 @@
         <v>1</v>
       </c>
       <c r="C33">
-        <v>35.453000000000003</v>
+        <f>C30*2</f>
+        <v>70.906000000000006</v>
       </c>
       <c r="D33">
         <f>D13</f>
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="1"/>
-        <v>102.8137</v>
+        <f t="shared" si="2"/>
+        <v>212.71800000000002</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3111,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48.61</v>
       </c>
     </row>
@@ -3161,11 +3600,12 @@
         <f>SUM(E20,E23,E25,E26)</f>
         <v>70.03</v>
       </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>18</v>
+      <c r="C39" s="2">
+        <v>70</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" ref="D39:D44" si="3">C39-B39</f>
+        <v>-3.0000000000001137E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -3176,11 +3616,12 @@
         <f>SUM(E21,E28)</f>
         <v>15.48685</v>
       </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
+      <c r="C40" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="3"/>
+        <v>1.3149999999999551E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -3195,7 +3636,7 @@
         <v>156.4</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" ref="D41:D44" si="2">C41-B41</f>
+        <f t="shared" si="3"/>
         <v>2.2800000000046339E-2</v>
       </c>
     </row>
@@ -3211,7 +3652,7 @@
         <v>160.30000000000001</v>
       </c>
       <c r="D42" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.2000000000000455E-2</v>
       </c>
     </row>
@@ -3227,7 +3668,7 @@
         <v>48.6</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-9.9999999999980105E-3</v>
       </c>
     </row>
@@ -3243,7 +3684,7 @@
         <v>64.099999999999994</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.0000000000001137E-2</v>
       </c>
     </row>
@@ -3252,7 +3693,115 @@
         <v>48</v>
       </c>
       <c r="B46" s="4">
-        <v>6</v>
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <f>B50*C50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <f>D4</f>
+        <v>0.6</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ref="D51:D54" si="4">B51*C51</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <f>D5</f>
+        <v>0.45</v>
+      </c>
+      <c r="D52">
+        <f>B52*C52*2</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f>D6</f>
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <f>D6</f>
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="7">
+        <f>IFERROR((D50+D53)/(D51+D52+D54), 0)</f>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -3262,7 +3811,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD89A06-016E-834C-9EF8-D374308C42E0}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
@@ -3301,12 +3850,12 @@
       <c r="C3">
         <v>115.3</v>
       </c>
-      <c r="D3">
-        <v>0</v>
+      <c r="D3" s="6">
+        <v>0.4</v>
       </c>
       <c r="E3" s="2">
         <f>IFERROR((C3*1000)/(1000/(B3*D3)), 0)</f>
-        <v>0</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3319,7 +3868,7 @@
       <c r="C4">
         <v>101.1</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="6">
         <v>0.6</v>
       </c>
       <c r="E4" s="2">
@@ -3337,7 +3886,7 @@
       <c r="C5">
         <v>164.08799999999999</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="6">
         <v>0.55000000000000004</v>
       </c>
       <c r="E5" s="2">
@@ -3355,12 +3904,12 @@
       <c r="C6">
         <v>80.043000000000006</v>
       </c>
-      <c r="D6">
-        <v>0.8</v>
+      <c r="D6" s="6">
+        <v>0.6</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>64.034400000000005</v>
+        <v>48.025799999999997</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -3400,11 +3949,11 @@
         <v>136.08600000000001</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>136.08600000000001</v>
+        <v>81.651600000000002</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -3418,11 +3967,11 @@
         <v>74.555000000000007</v>
       </c>
       <c r="D11">
-        <v>1.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>134.19900000000001</v>
+        <v>164.02100000000002</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3436,11 +3985,11 @@
         <v>100.087</v>
       </c>
       <c r="D12">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>40.034799999999997</v>
+        <v>20.017399999999999</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3454,11 +4003,11 @@
         <v>110.98</v>
       </c>
       <c r="D13">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>277.45</v>
+        <v>299.64600000000002</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3549,11 +4098,11 @@
       </c>
       <c r="D20">
         <f>D3</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="2">
-        <f>IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
-        <v>0</v>
+        <f t="shared" ref="E20:E31" si="1">IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
+        <v>5.6024000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3568,11 +4117,11 @@
       </c>
       <c r="D21">
         <f>D3</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E21" s="2">
-        <f>IFERROR((C21*1000)/(1000/(B21*D21)), 0)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>12.389480000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3590,7 +4139,7 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="2">
-        <f>IFERROR((C22*1000)/(1000/(B22*D22)), 0)</f>
+        <f t="shared" si="1"/>
         <v>46.913159999999991</v>
       </c>
     </row>
@@ -3609,7 +4158,7 @@
         <v>0.6</v>
       </c>
       <c r="E23" s="2">
-        <f>IFERROR((C23*1000)/(1000/(B23*D23)), 0)</f>
+        <f t="shared" si="1"/>
         <v>16.807199999999998</v>
       </c>
     </row>
@@ -3628,7 +4177,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E24" s="2">
-        <f>IFERROR((C24*1000)/(1000/(B24*D24)), 0)</f>
+        <f t="shared" si="1"/>
         <v>44.085800000000006</v>
       </c>
     </row>
@@ -3647,7 +4196,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E25" s="2">
-        <f>IFERROR((C25*1000)/(1000/(B25*D25)), 0)</f>
+        <f t="shared" si="1"/>
         <v>30.813200000000002</v>
       </c>
     </row>
@@ -3663,11 +4212,11 @@
       </c>
       <c r="D26">
         <f>D6</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E26" s="2">
-        <f>IFERROR((C26*1000)/(1000/(B26*D26)), 0)</f>
-        <v>22.409600000000001</v>
+        <f t="shared" si="1"/>
+        <v>16.807199999999998</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3682,11 +4231,11 @@
       </c>
       <c r="D27">
         <f>D10</f>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E27" s="2">
-        <f>IFERROR((C27*1000)/(1000/(B27*D27)), 0)</f>
-        <v>39.094299999999997</v>
+        <f t="shared" si="1"/>
+        <v>23.456579999999995</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3701,11 +4250,11 @@
       </c>
       <c r="D28">
         <f>D10</f>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E28" s="2">
-        <f>IFERROR((C28*1000)/(1000/(B28*D28)), 0)</f>
-        <v>30.973700000000001</v>
+        <f t="shared" si="1"/>
+        <v>18.584219999999998</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -3720,11 +4269,11 @@
       </c>
       <c r="D29">
         <f>D11</f>
-        <v>1.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E29" s="2">
-        <f>IFERROR((C29*1000)/(1000/(B29*D29)), 0)</f>
-        <v>70.369739999999993</v>
+        <f t="shared" si="1"/>
+        <v>86.007459999999995</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -3739,11 +4288,11 @@
       </c>
       <c r="D30">
         <f>D11</f>
-        <v>1.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E30" s="2">
-        <f>IFERROR((C30*1000)/(1000/(B30*D30)), 0)</f>
-        <v>63.815400000000004</v>
+        <f t="shared" si="1"/>
+        <v>77.996600000000001</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3758,11 +4307,11 @@
       </c>
       <c r="D31">
         <f>D12</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E31" s="2">
-        <f>IFERROR((C31*1000)/(1000/(B31*D31)), 0)</f>
-        <v>16.031199999999998</v>
+        <f t="shared" si="1"/>
+        <v>8.0155999999999992</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -3777,11 +4326,11 @@
       </c>
       <c r="D32">
         <f>D13</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32:E34" si="1">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
-        <v>100.19499999999999</v>
+        <f t="shared" ref="E32:E34" si="2">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
+        <v>108.21060000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -3792,15 +4341,16 @@
         <v>1</v>
       </c>
       <c r="C33">
-        <v>35.453000000000003</v>
+        <f>C30*2</f>
+        <v>70.906000000000006</v>
       </c>
       <c r="D33">
         <f>D13</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="1"/>
-        <v>88.632499999999993</v>
+        <f t="shared" si="2"/>
+        <v>191.44620000000003</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -3818,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48.61</v>
       </c>
     </row>
@@ -3868,11 +4418,12 @@
         <f>SUM(E20,E23,E25,E26)</f>
         <v>70.03</v>
       </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>18</v>
+      <c r="C39" s="2">
+        <v>70</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" ref="D39:D44" si="3">C39-B39</f>
+        <v>-3.0000000000001137E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -3883,11 +4434,12 @@
         <f>SUM(E21,E28)</f>
         <v>30.973700000000001</v>
       </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
+      <c r="C40" s="2">
+        <v>31</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="3"/>
+        <v>2.6299999999999102E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -3902,7 +4454,7 @@
         <v>156.4</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" ref="D41:D44" si="2">C41-B41</f>
+        <f t="shared" si="3"/>
         <v>2.2800000000046339E-2</v>
       </c>
     </row>
@@ -3918,7 +4470,7 @@
         <v>160.30000000000001</v>
       </c>
       <c r="D42" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.2000000000000455E-2</v>
       </c>
     </row>
@@ -3934,7 +4486,7 @@
         <v>48.6</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-9.9999999999980105E-3</v>
       </c>
     </row>
@@ -3950,7 +4502,7 @@
         <v>64.099999999999994</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.0000000000001137E-2</v>
       </c>
     </row>
@@ -3958,8 +4510,116 @@
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="4">
-        <v>6.1</v>
+      <c r="B46" s="9">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <f>D3</f>
+        <v>0.4</v>
+      </c>
+      <c r="D50">
+        <f>B50*C50</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <f>D4</f>
+        <v>0.6</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ref="D51:D54" si="4">B51*C51</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <f>D5</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D52">
+        <f>B52*C52*2</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f>D6</f>
+        <v>0.6</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <f>D6</f>
+        <v>0.6</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="7">
+        <f>IFERROR((D50+D53)/(D51+D52+D54), 0)</f>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -3968,8 +4628,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D19AFD18-DA23-7543-8823-72036396CBF7}">
-  <dimension ref="A1:E46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867B7B44-52D0-4D44-AF95-1551EAF5830D}">
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
@@ -4009,11 +4669,11 @@
         <v>115.3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E3" s="2">
         <f>IFERROR((C3*1000)/(1000/(B3*D3)), 0)</f>
-        <v>0</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4063,11 +4723,11 @@
         <v>80.043000000000006</v>
       </c>
       <c r="D6">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>64.034400000000005</v>
+        <v>48.025799999999997</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -4107,11 +4767,11 @@
         <v>136.08600000000001</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>272.17200000000003</v>
+        <v>149.69460000000001</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -4125,11 +4785,11 @@
         <v>74.555000000000007</v>
       </c>
       <c r="D11">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>59.643999999999998</v>
+        <v>126.7435</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4143,11 +4803,11 @@
         <v>100.087</v>
       </c>
       <c r="D12">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>60.052199999999999</v>
+        <v>30.0261</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4161,11 +4821,11 @@
         <v>110.98</v>
       </c>
       <c r="D13">
-        <v>2.2999999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>255.25399999999999</v>
+        <v>288.548</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4256,11 +4916,11 @@
       </c>
       <c r="D20">
         <f>D3</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="2">
-        <f>IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
-        <v>0</v>
+        <f t="shared" ref="E20:E31" si="1">IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
+        <v>5.6024000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4275,11 +4935,11 @@
       </c>
       <c r="D21">
         <f>D3</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E21" s="2">
-        <f>IFERROR((C21*1000)/(1000/(B21*D21)), 0)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>12.389480000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4297,7 +4957,7 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="2">
-        <f>IFERROR((C22*1000)/(1000/(B22*D22)), 0)</f>
+        <f t="shared" si="1"/>
         <v>46.913159999999991</v>
       </c>
     </row>
@@ -4316,7 +4976,7 @@
         <v>0.6</v>
       </c>
       <c r="E23" s="2">
-        <f>IFERROR((C23*1000)/(1000/(B23*D23)), 0)</f>
+        <f t="shared" si="1"/>
         <v>16.807199999999998</v>
       </c>
     </row>
@@ -4335,7 +4995,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E24" s="2">
-        <f>IFERROR((C24*1000)/(1000/(B24*D24)), 0)</f>
+        <f t="shared" si="1"/>
         <v>44.085800000000006</v>
       </c>
     </row>
@@ -4354,7 +5014,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E25" s="2">
-        <f>IFERROR((C25*1000)/(1000/(B25*D25)), 0)</f>
+        <f t="shared" si="1"/>
         <v>30.813200000000002</v>
       </c>
     </row>
@@ -4370,11 +5030,11 @@
       </c>
       <c r="D26">
         <f>D6</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E26" s="2">
-        <f>IFERROR((C26*1000)/(1000/(B26*D26)), 0)</f>
-        <v>22.409600000000001</v>
+        <f t="shared" si="1"/>
+        <v>16.807199999999998</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4389,11 +5049,11 @@
       </c>
       <c r="D27">
         <f>D10</f>
-        <v>2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E27" s="2">
-        <f>IFERROR((C27*1000)/(1000/(B27*D27)), 0)</f>
-        <v>78.188599999999994</v>
+        <f t="shared" si="1"/>
+        <v>43.003729999999997</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4408,11 +5068,11 @@
       </c>
       <c r="D28">
         <f>D10</f>
-        <v>2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E28" s="2">
-        <f>IFERROR((C28*1000)/(1000/(B28*D28)), 0)</f>
-        <v>61.947400000000002</v>
+        <f t="shared" si="1"/>
+        <v>34.071070000000006</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -4427,11 +5087,11 @@
       </c>
       <c r="D29">
         <f>D11</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="E29" s="2">
-        <f>IFERROR((C29*1000)/(1000/(B29*D29)), 0)</f>
-        <v>31.275439999999996</v>
+        <f t="shared" si="1"/>
+        <v>66.460309999999993</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -4446,11 +5106,11 @@
       </c>
       <c r="D30">
         <f>D11</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="E30" s="2">
-        <f>IFERROR((C30*1000)/(1000/(B30*D30)), 0)</f>
-        <v>28.362400000000001</v>
+        <f t="shared" si="1"/>
+        <v>60.270099999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4465,11 +5125,11 @@
       </c>
       <c r="D31">
         <f>D12</f>
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E31" s="2">
-        <f>IFERROR((C31*1000)/(1000/(B31*D31)), 0)</f>
-        <v>24.046799999999998</v>
+        <f t="shared" si="1"/>
+        <v>12.023399999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -4484,11 +5144,11 @@
       </c>
       <c r="D32">
         <f>D13</f>
-        <v>2.2999999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32:E34" si="1">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
-        <v>92.179400000000001</v>
+        <f t="shared" ref="E32:E34" si="2">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
+        <v>104.20280000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -4499,15 +5159,16 @@
         <v>1</v>
       </c>
       <c r="C33">
-        <v>35.453000000000003</v>
+        <f>C30*2</f>
+        <v>70.906000000000006</v>
       </c>
       <c r="D33">
         <f>D13</f>
-        <v>2.2999999999999998</v>
+        <v>2.6</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="1"/>
-        <v>81.541899999999998</v>
+        <f t="shared" si="2"/>
+        <v>184.35560000000001</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4525,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48.61</v>
       </c>
     </row>
@@ -4575,11 +5236,12 @@
         <f>SUM(E20,E23,E25,E26)</f>
         <v>70.03</v>
       </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>18</v>
+      <c r="C39">
+        <v>70</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" ref="D39:D44" si="3">C39-B39</f>
+        <v>-3.0000000000001137E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -4588,13 +5250,14 @@
       </c>
       <c r="B40" s="2">
         <f>SUM(E21,E28)</f>
-        <v>61.947400000000002</v>
-      </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
+        <v>46.460550000000005</v>
+      </c>
+      <c r="C40">
+        <v>46.5</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="3"/>
+        <v>3.94499999999951E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -4609,7 +5272,7 @@
         <v>156.4</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" ref="D41:D44" si="2">C41-B41</f>
+        <f t="shared" si="3"/>
         <v>2.2800000000017917E-2</v>
       </c>
     </row>
@@ -4625,7 +5288,7 @@
         <v>160.30000000000001</v>
       </c>
       <c r="D42" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.2000000000000455E-2</v>
       </c>
     </row>
@@ -4641,7 +5304,7 @@
         <v>48.6</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-9.9999999999980105E-3</v>
       </c>
     </row>
@@ -4657,7 +5320,7 @@
         <v>64.099999999999994</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.0000000000001137E-2</v>
       </c>
     </row>
@@ -4667,6 +5330,114 @@
       </c>
       <c r="B46" s="4">
         <v>6.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <f>D3</f>
+        <v>0.4</v>
+      </c>
+      <c r="D50">
+        <f>B50*C50</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <f>D4</f>
+        <v>0.6</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ref="D51:D54" si="4">B51*C51</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <f>D5</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D52">
+        <f>B52*C52*2</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f>D6</f>
+        <v>0.6</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <f>D6</f>
+        <v>0.6</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="7">
+        <f>IFERROR((D50+D53)/(D51+D52+D54), 0)</f>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -4675,8 +5446,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867B7B44-52D0-4D44-AF95-1551EAF5830D}">
-  <dimension ref="A1:E46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D19AFD18-DA23-7543-8823-72036396CBF7}">
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
@@ -4716,11 +5487,11 @@
         <v>115.3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E3" s="2">
         <f>IFERROR((C3*1000)/(1000/(B3*D3)), 0)</f>
-        <v>0</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4770,11 +5541,11 @@
         <v>80.043000000000006</v>
       </c>
       <c r="D6">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>64.034400000000005</v>
+        <v>48.025799999999997</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -4814,11 +5585,11 @@
         <v>136.08600000000001</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>408.25800000000004</v>
+        <v>217.73759999999999</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -4832,11 +5603,11 @@
         <v>74.555000000000007</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>89.465999999999994</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4850,11 +5621,11 @@
         <v>100.087</v>
       </c>
       <c r="D12">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>50.043500000000002</v>
+        <v>20.017399999999999</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4868,11 +5639,11 @@
         <v>110.98</v>
       </c>
       <c r="D13">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>266.35199999999998</v>
+        <v>299.64600000000002</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4963,11 +5734,11 @@
       </c>
       <c r="D20">
         <f>D3</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="2">
-        <f>IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
-        <v>0</v>
+        <f t="shared" ref="E20:E31" si="1">IFERROR((C20*1000)/(1000/(B20*D20)), 0)</f>
+        <v>5.6024000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -4982,11 +5753,11 @@
       </c>
       <c r="D21">
         <f>D3</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E21" s="2">
-        <f>IFERROR((C21*1000)/(1000/(B21*D21)), 0)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>12.389480000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -5004,7 +5775,7 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="2">
-        <f>IFERROR((C22*1000)/(1000/(B22*D22)), 0)</f>
+        <f t="shared" si="1"/>
         <v>46.913159999999991</v>
       </c>
     </row>
@@ -5023,7 +5794,7 @@
         <v>0.6</v>
       </c>
       <c r="E23" s="2">
-        <f>IFERROR((C23*1000)/(1000/(B23*D23)), 0)</f>
+        <f t="shared" si="1"/>
         <v>16.807199999999998</v>
       </c>
     </row>
@@ -5042,7 +5813,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E24" s="2">
-        <f>IFERROR((C24*1000)/(1000/(B24*D24)), 0)</f>
+        <f t="shared" si="1"/>
         <v>44.085800000000006</v>
       </c>
     </row>
@@ -5061,7 +5832,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E25" s="2">
-        <f>IFERROR((C25*1000)/(1000/(B25*D25)), 0)</f>
+        <f t="shared" si="1"/>
         <v>30.813200000000002</v>
       </c>
     </row>
@@ -5077,11 +5848,11 @@
       </c>
       <c r="D26">
         <f>D6</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E26" s="2">
-        <f>IFERROR((C26*1000)/(1000/(B26*D26)), 0)</f>
-        <v>22.409600000000001</v>
+        <f t="shared" si="1"/>
+        <v>16.807199999999998</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -5096,11 +5867,11 @@
       </c>
       <c r="D27">
         <f>D10</f>
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E27" s="2">
-        <f>IFERROR((C27*1000)/(1000/(B27*D27)), 0)</f>
-        <v>117.2829</v>
+        <f t="shared" si="1"/>
+        <v>62.550879999999992</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -5115,11 +5886,11 @@
       </c>
       <c r="D28">
         <f>D10</f>
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="E28" s="2">
-        <f>IFERROR((C28*1000)/(1000/(B28*D28)), 0)</f>
-        <v>92.92110000000001</v>
+        <f t="shared" si="1"/>
+        <v>49.557920000000003</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -5134,11 +5905,11 @@
       </c>
       <c r="D29">
         <f>D11</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E29" s="2">
-        <f>IFERROR((C29*1000)/(1000/(B29*D29)), 0)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>46.913159999999991</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -5153,11 +5924,11 @@
       </c>
       <c r="D30">
         <f>D11</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E30" s="2">
-        <f>IFERROR((C30*1000)/(1000/(B30*D30)), 0)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>42.543599999999998</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -5172,11 +5943,11 @@
       </c>
       <c r="D31">
         <f>D12</f>
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E31" s="2">
-        <f>IFERROR((C31*1000)/(1000/(B31*D31)), 0)</f>
-        <v>20.039000000000001</v>
+        <f t="shared" si="1"/>
+        <v>8.0155999999999992</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -5191,11 +5962,11 @@
       </c>
       <c r="D32">
         <f>D13</f>
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32:E34" si="1">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
-        <v>96.18719999999999</v>
+        <f t="shared" ref="E32:E34" si="2">IFERROR((C32*1000)/(1000/(B32*D32)), 0)</f>
+        <v>108.21060000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -5206,15 +5977,16 @@
         <v>1</v>
       </c>
       <c r="C33">
-        <v>35.453000000000003</v>
+        <f>C30*2</f>
+        <v>70.906000000000006</v>
       </c>
       <c r="D33">
         <f>D13</f>
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="1"/>
-        <v>85.087199999999996</v>
+        <f t="shared" si="2"/>
+        <v>191.44620000000003</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" x14ac:dyDescent="0.25">
@@ -5232,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48.61</v>
       </c>
     </row>
@@ -5268,7 +6040,7 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
@@ -5282,11 +6054,12 @@
         <f>SUM(E20,E23,E25,E26)</f>
         <v>70.03</v>
       </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>18</v>
+      <c r="C39" s="2">
+        <v>70</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" ref="D39:D44" si="3">C39-B39</f>
+        <v>-3.0000000000001137E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -5295,13 +6068,14 @@
       </c>
       <c r="B40" s="2">
         <f>SUM(E21,E28)</f>
-        <v>92.92110000000001</v>
-      </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
+        <v>61.947400000000002</v>
+      </c>
+      <c r="C40" s="2">
+        <v>62</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="3"/>
+        <v>5.2599999999998204E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -5310,14 +6084,14 @@
       </c>
       <c r="B41" s="2">
         <f>SUM(E22,E27,E29)</f>
-        <v>164.19605999999999</v>
+        <v>156.37719999999996</v>
       </c>
       <c r="C41">
         <v>156.4</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" ref="D41:D44" si="2">C41-B41</f>
-        <v>-7.7960599999999829</v>
+        <f t="shared" si="3"/>
+        <v>2.2800000000046339E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -5332,7 +6106,7 @@
         <v>160.30000000000001</v>
       </c>
       <c r="D42" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.2000000000000455E-2</v>
       </c>
     </row>
@@ -5348,7 +6122,7 @@
         <v>48.6</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-9.9999999999980105E-3</v>
       </c>
     </row>
@@ -5364,7 +6138,7 @@
         <v>64.099999999999994</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.0000000000001137E-2</v>
       </c>
     </row>
@@ -5374,6 +6148,114 @@
       </c>
       <c r="B46" s="4">
         <v>6.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <f>D3</f>
+        <v>0.4</v>
+      </c>
+      <c r="D50">
+        <f>B50*C50</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <f>D4</f>
+        <v>0.6</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ref="D51:D54" si="4">B51*C51</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <f>D5</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D52">
+        <f>B52*C52*2</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f>D6</f>
+        <v>0.6</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <f>D6</f>
+        <v>0.6</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="7">
+        <f>IFERROR((D50+D53)/(D51+D52+D54), 0)</f>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
